--- a/Excel Practice @ Day 06.xlsx
+++ b/Excel Practice @ Day 06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MY FILES\M S Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACEB6E7-FF1E-4253-B0A2-C159741FAFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6007AA-FF26-4A55-8D3F-7C55D428218D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E03010A2-10A4-4CD2-AD45-567A05CD1053}"/>
   </bookViews>
